--- a/code/files/eigh_catalogos.xlsx
+++ b/code/files/eigh_catalogos.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="entidades" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="claves_gasto" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="notas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="rubros_texto" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="notas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t xml:space="preserve">Catálogo de entidades federativas</t>
   </si>
@@ -142,10 +143,58 @@
     <t xml:space="preserve">Ropa, calzado y accesorios</t>
   </si>
   <si>
+    <t xml:space="preserve">Clasificación del gasto - captura de campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rubro_completo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A001 - Alimentos consumidos dentro del hogar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">necesario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A002 – ALIMENTOS CONSUMIDOS FUERA DEL HOGAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">discrecional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  B001- Renta o pago de vivienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NECESARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B002 : Electricidad,  agua y combustible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necesario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C001 - transporte público y particular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D001  -  Colegiaturas y material escolar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">E001- CONSULTAS, medicamentos y hospitalización</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F001 – Ropa, calzado y accesorios  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discrecional</t>
+  </si>
+  <si>
     <t xml:space="preserve">Notas metodológicas</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">1. Los montos son trimestrales y están expresados en pesos corrientes.</t>
@@ -680,13 +729,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>43</v>
-      </c>
-    </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
         <v>44</v>
       </c>
     </row>
@@ -694,10 +741,100 @@
       <c r="A4" t="s">
         <v>45</v>
       </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
